--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BA0EB6F-76C9-4B69-9F9C-4999CA383373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5253B4D-8003-411D-8D81-3FCBA04FE837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="128">
   <si>
     <t>Story ID</t>
   </si>
@@ -95,12 +95,6 @@
     <t>AQU2</t>
   </si>
   <si>
-    <t>Fische</t>
-  </si>
-  <si>
-    <t>Als Nutzer möchte ich Fische in meinem Aquarium schwimmen sehen.</t>
-  </si>
-  <si>
     <t>AQU3</t>
   </si>
   <si>
@@ -426,13 +420,37 @@
   </si>
   <si>
     <t>Efford/Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquarium </t>
+  </si>
+  <si>
+    <t>Aquarium Anzeigen</t>
+  </si>
+  <si>
+    <t>Wasser und Effeckte</t>
+  </si>
+  <si>
+    <t>Ein Aquarium ist vorhanden</t>
+  </si>
+  <si>
+    <t>Wasser befindet sich im aquarium wellen/blasen bewegen sich</t>
+  </si>
+  <si>
+    <t>Buttons für Licht/Füttern..</t>
+  </si>
+  <si>
+    <t>Fisch</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich Fisch in meinem Aquarium schwimmen sehen.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +509,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -530,7 +555,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -538,11 +563,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -557,11 +594,493 @@
     <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="41">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -604,383 +1123,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -995,30 +1137,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1074,25 +1192,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -1113,6 +1212,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1160,6 +1260,49 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1177,26 +1320,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:I8" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:I8" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:I8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="36">
       <calculatedColumnFormula array="1">Tabelle3[Estimated time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="35">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="34">
+      <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="33">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="26">
+    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="31">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6DE4E5A9-9F01-4F4D-9656-9EB637B780BA}" name="Estimated Time" dataDxfId="25">
+    <tableColumn id="8" xr3:uid="{6DE4E5A9-9F01-4F4D-9656-9EB637B780BA}" name="Estimated Time" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1205,35 +1350,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J7" insertRowShift="1" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:J7" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
+  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A13:C14" totalsRowShown="0" headerRowDxfId="3" dataDxfId="7">
-  <autoFilter ref="A13:C14" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="15">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="14">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="13">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1241,14 +1402,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E13:F14" totalsRowShown="0" headerRowDxfId="2" dataDxfId="4">
-  <autoFilter ref="E13:F14" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="10">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="9">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1598,43 +1759,44 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" s="7" cm="1">
         <f t="array" ref="C2">Tabelle3[Estimated time]</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D2" s="7" cm="1">
         <f t="array" ref="D2">Tabelle3[Actual time]</f>
-        <v>9</v>
-      </c>
-      <c r="E2" s="7">
+        <v>17</v>
+      </c>
+      <c r="E2" s="7" cm="1">
+        <f t="array" ref="E2">Tabelle4[[Total Storypoints ]]</f>
         <v>0</v>
       </c>
       <c r="F2" s="7">
@@ -1655,7 +1817,7 @@
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1677,7 +1839,7 @@
     </row>
     <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1699,7 +1861,7 @@
     </row>
     <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1721,7 +1883,7 @@
     </row>
     <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A6" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1743,7 +1905,7 @@
     </row>
     <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1765,7 +1927,7 @@
     </row>
     <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.5">
       <c r="A8" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1787,7 +1949,7 @@
     </row>
     <row r="13" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C13" s="5">
         <v>141</v>
@@ -1795,7 +1957,7 @@
     </row>
     <row r="14" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" s="5">
         <f>COUNTIF(Tabelle1[Sprint],"*Sprint*")</f>
@@ -1804,7 +1966,7 @@
     </row>
     <row r="15" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
@@ -1813,9 +1975,9 @@
     </row>
     <row r="16" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="5">
+        <v>95</v>
+      </c>
+      <c r="C16" s="14">
         <f>(SUM(Tabelle1[Accomplished Story Points],)/G2)</f>
         <v>0</v>
       </c>
@@ -1834,19 +1996,19 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1863,21 +2025,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -1888,20 +2051,23 @@
       <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -1910,19 +2076,20 @@
         <v>8</v>
       </c>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
@@ -1931,19 +2098,20 @@
         <v>3</v>
       </c>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="2">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
@@ -1952,19 +2120,20 @@
         <v>5</v>
       </c>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2">
+        <v>17</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>9</v>
@@ -1973,19 +2142,20 @@
         <v>4</v>
       </c>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>9</v>
@@ -1994,19 +2164,20 @@
         <v>6</v>
       </c>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
@@ -2015,19 +2186,20 @@
         <v>7</v>
       </c>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
@@ -2036,19 +2208,20 @@
         <v>4</v>
       </c>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="2">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
@@ -2057,19 +2230,20 @@
         <v>8</v>
       </c>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>9</v>
@@ -2078,19 +2252,20 @@
         <v>5</v>
       </c>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
@@ -2099,19 +2274,20 @@
         <v>6</v>
       </c>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B13" s="2">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
@@ -2120,19 +2296,20 @@
         <v>3</v>
       </c>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B14" s="2">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>9</v>
@@ -2141,19 +2318,20 @@
         <v>7</v>
       </c>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B15" s="2">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>9</v>
@@ -2162,19 +2340,20 @@
         <v>4</v>
       </c>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B16" s="2">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>9</v>
@@ -2183,19 +2362,20 @@
         <v>5</v>
       </c>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B17" s="2">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>9</v>
@@ -2204,19 +2384,20 @@
         <v>8</v>
       </c>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B18" s="2">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>9</v>
@@ -2225,19 +2406,20 @@
         <v>6</v>
       </c>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>9</v>
@@ -2246,19 +2428,20 @@
         <v>3</v>
       </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B20" s="2">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>9</v>
@@ -2267,19 +2450,20 @@
         <v>5</v>
       </c>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B21" s="2">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>9</v>
@@ -2288,19 +2472,20 @@
         <v>9</v>
       </c>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B22" s="2">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>9</v>
@@ -2309,19 +2494,20 @@
         <v>4</v>
       </c>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="2">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>9</v>
@@ -2330,19 +2516,20 @@
         <v>9</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B24" s="2">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>9</v>
@@ -2351,19 +2538,20 @@
         <v>6</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B25" s="2">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>9</v>
@@ -2372,19 +2560,20 @@
         <v>4</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="2">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B26" s="2">
-        <v>16</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>9</v>
@@ -2393,10 +2582,11 @@
         <v>7</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -2408,6 +2598,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2416,51 +2609,51 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="94.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
@@ -2471,23 +2664,23 @@
         <v>45932</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G2" s="8">
         <v>2</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J2" s="8">
         <v>2</v>
@@ -2497,18 +2690,18 @@
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G3" s="8">
         <v>4</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8">
@@ -2519,12 +2712,12 @@
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -2550,38 +2743,80 @@
     <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="8">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="J7" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="J8" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="8"/>
@@ -2632,53 +2867,77 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>113</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>121</v>
-      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="12">
-        <f>SUM(Tabelle2[Estimated time])</f>
-        <v>7</v>
-      </c>
-      <c r="B14" s="12">
-        <f>SUM(Tabelle2[Time in Hours])</f>
-        <v>9</v>
-      </c>
-      <c r="C14" s="12">
-        <f>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</f>
-        <v>-2</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="12">
-        <f>SUM(Tabelle2[Story points])</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="12">
-        <f>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</f>
-        <v>0</v>
-      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="12">
+        <f>SUM(Tabelle2[Estimated time])</f>
+        <v>13</v>
+      </c>
+      <c r="B16" s="12">
+        <f>SUM(Tabelle2[Time in Hours])</f>
+        <v>17</v>
+      </c>
+      <c r="C16" s="12">
+        <f>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</f>
+        <v>-4</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="12">
+        <f>SUM(Tabelle2[Story points])</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <f>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5253B4D-8003-411D-8D81-3FCBA04FE837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C83BDA-0CDC-466B-909D-6F92D22E2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
-    <sheet name="Storys" sheetId="1" r:id="rId2"/>
-    <sheet name="Sprint1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sprint1" sheetId="3" r:id="rId2"/>
+    <sheet name="Storys" sheetId="1" r:id="rId3"/>
+    <sheet name="Sprint2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="138">
   <si>
     <t>Story ID</t>
   </si>
@@ -101,9 +102,6 @@
     <t>Grundfunktionen</t>
   </si>
   <si>
-    <t>Als Nutzer möchte ich Fische füttern können.</t>
-  </si>
-  <si>
     <t>AQU4</t>
   </si>
   <si>
@@ -444,6 +442,39 @@
   </si>
   <si>
     <t>Als Nutzer möchte ich Fisch in meinem Aquarium schwimmen sehen.</t>
+  </si>
+  <si>
+    <t>Monitoring/AQU1</t>
+  </si>
+  <si>
+    <t>Wasser befindet sich im aquarium wellen oben / steine/erde am boden?</t>
+  </si>
+  <si>
+    <t>Handyansicht</t>
+  </si>
+  <si>
+    <t>Ansicht im Handyformat</t>
+  </si>
+  <si>
+    <t>Profilverwaltung/Anlegen</t>
+  </si>
+  <si>
+    <t>Als nutzer möchte ich mich anmelden und "mein" Aquarium haben</t>
+  </si>
+  <si>
+    <t>Story Points left</t>
+  </si>
+  <si>
+    <t>Pflanzen</t>
+  </si>
+  <si>
+    <t>Als nutzer möchte ich Pflanzen in mein Aquarium Setzen</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte "mein" Aquarium haben</t>
   </si>
 </sst>
 </file>
@@ -579,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -595,15 +626,830 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="61">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF0F9ED5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF0F9ED5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -633,6 +1479,14 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -655,431 +1509,6 @@
           <bgColor theme="3" tint="0.499984740745262"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1113,46 +1542,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1320,29 +1709,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:I8" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A1:I8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+  <autoFilter ref="A1:H8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="56">
       <calculatedColumnFormula array="1">Tabelle3[Estimated time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="35">
+    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="55">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="0">
       <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="54">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="31">
+    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="52">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{6DE4E5A9-9F01-4F4D-9656-9EB637B780BA}" name="Estimated Time" dataDxfId="30">
-      <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1350,51 +1736,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
-  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="18"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="28">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="14">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="27">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="13">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="26">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1402,15 +1772,83 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="23">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="22">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="43"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="7">
+      <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="6">
+      <calculatedColumnFormula>SUM(Tabelle27[Time in Hours])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="5">
+      <calculatedColumnFormula>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="2">
+      <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="1">
+      <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1737,7 +2175,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -1751,7 +2189,7 @@
     <col min="9" max="9" width="22.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -1759,33 +2197,30 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+      <c r="A2" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="7" cm="1">
         <f t="array" ref="C2">Tabelle3[Estimated time]</f>
@@ -1804,42 +2239,47 @@
         <v>0</v>
       </c>
       <c r="G2" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H2" s="7">
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
-        <v>141</v>
-      </c>
-      <c r="I2" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+        <v>86</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="7" cm="1">
+        <f t="array" ref="C3">Tabelle38[Estimated time]</f>
+        <v>12</v>
+      </c>
+      <c r="D3" s="7" cm="1">
+        <f t="array" ref="D3">Tabelle38[Actual time]</f>
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" cm="1">
+        <f t="array" ref="E3">Tabelle49[[Total Storypoints ]]</f>
+        <v>13</v>
+      </c>
       <c r="F3" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>1.4444444444444444</v>
+      </c>
+      <c r="G3" s="7">
+        <v>146</v>
+      </c>
       <c r="H3" s="7">
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1854,14 +2294,10 @@
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
         <v>0</v>
       </c>
-      <c r="I4" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+    </row>
+    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1876,14 +2312,10 @@
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
         <v>0</v>
       </c>
-      <c r="I5" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+    </row>
+    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A6" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1898,14 +2330,10 @@
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
         <v>0</v>
       </c>
-      <c r="I6" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+    </row>
+    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1920,14 +2348,10 @@
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
         <v>0</v>
       </c>
-      <c r="I7" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.5">
+    </row>
+    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A8" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1942,44 +2366,58 @@
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
         <v>0</v>
       </c>
-      <c r="I8" s="7">
-        <f>IFERROR(Tabelle1[[#This Row],[Storypoints Left]]/Tabelle1[[#This Row],[Velocity]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C13" s="5">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <f>C12-SUM(Tabelle1[Accomplished Story Points])</f>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="5">
         <f>COUNTIF(Tabelle1[Sprint],"*Sprint*")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.20634920634920634</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="14">
         <f>(SUM(Tabelle1[Accomplished Story Points],)/G2)</f>
-        <v>0</v>
+        <v>8.9041095890410954E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="18">
+        <f>C13/C15</f>
+        <v>644.53846153846155</v>
       </c>
     </row>
   </sheetData>
@@ -1992,619 +2430,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
-  <sheetPr>
-    <tabColor theme="6"/>
-  </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="I3" s="17"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="I4" s="17"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="2">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="2">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="I17" s="17"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="2">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="2">
-        <v>14</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="2">
-        <v>4</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="2">
-        <v>15</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="2">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="2">
-        <v>7</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="2">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="2">
-        <v>16</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2">
-        <v>7</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4">
-        <f>SUM(F2:F26)</f>
-        <v>141</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9241CD9D-70AE-44DD-9C82-08638998B9B7}">
   <sheetPr>
     <tabColor theme="0"/>
@@ -2626,34 +2451,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
@@ -2664,23 +2489,23 @@
         <v>45932</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G2" s="8">
         <v>2</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="8">
         <v>2</v>
@@ -2690,18 +2515,18 @@
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G3" s="8">
         <v>4</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8">
@@ -2712,12 +2537,12 @@
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -2744,22 +2569,22 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="G6" s="8">
         <v>2</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I6" s="8">
         <v>0</v>
@@ -2772,22 +2597,22 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" s="8">
         <v>3</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8">
@@ -2798,16 +2623,16 @@
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
@@ -2892,20 +2717,20 @@
     </row>
     <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>110</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>111</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -2947,4 +2772,948 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <f>SUM(F2:F26)</f>
+        <v>146</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90405E51-A006-46BC-8B15-C0222E7D47D2}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>45939</v>
+      </c>
+      <c r="B2" s="9">
+        <v>45953</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="10">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="8">
+        <v>5</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="8">
+        <v>8</v>
+      </c>
+      <c r="J5" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="8">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="12">
+        <f>SUM(Tabelle27[Estimated time])</f>
+        <v>12</v>
+      </c>
+      <c r="B16" s="12">
+        <f>SUM(Tabelle27[Time in Hours])</f>
+        <v>9</v>
+      </c>
+      <c r="C16" s="12">
+        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="12">
+        <f>SUM(Tabelle27[Story points])</f>
+        <v>13</v>
+      </c>
+      <c r="F16" s="12">
+        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
+        <v>1.4444444444444444</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhoheneder/Desktop/Schule/syp/AquaSphere/Excel_File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C83BDA-0CDC-466B-909D-6F92D22E2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C95B2-D4F4-7C4E-AC15-9845565D49EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="1340" yWindow="1020" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Storys" sheetId="1" r:id="rId3"/>
     <sheet name="Sprint2" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="148">
   <si>
     <t>Story ID</t>
   </si>
@@ -475,13 +474,43 @@
   </si>
   <si>
     <t>Als Nutzer möchte "mein" Aquarium haben</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>Effort/Hour</t>
+  </si>
+  <si>
+    <t>Started / not done</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Backend mit Datenbank erstellen</t>
+  </si>
+  <si>
+    <t>Datenbank und Backend erstellt und einsatzbereit</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Zustand speichern und korrekt mit User verknüpfen</t>
+  </si>
+  <si>
+    <t>Zustände müssen universell für offline und online speicherung erstellt werden. Online zustände werden ans Backend übertragen und korrekt mit dem User abgespeichert</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Offline und Online zustände korrekt handlen</t>
+  </si>
+  <si>
+    <t>Wenn der User einsteigt wird überprüft welcher Speicherstand der aktuellste ist und dieser dann heruntergeladen / hochgeladen</t>
+  </si>
+  <si>
+    <t>in progress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +576,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -610,7 +645,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -630,31 +665,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="61">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
+  <dxfs count="62">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1017,383 +1047,6 @@
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -1512,6 +1165,383 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1542,6 +1572,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1709,18 +1759,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
   <autoFilter ref="A1:H8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="57">
       <calculatedColumnFormula array="1">Tabelle3[Estimated time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="55">
+    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="56">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="55">
       <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="54">
@@ -1736,35 +1786,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="37">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="27">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="36">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="35">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1773,13 +1823,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="32">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="31">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1788,25 +1838,25 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:K12" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:K12" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="17"/>
@@ -1817,14 +1867,15 @@
     <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
     <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="11"/>
     <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{EEDB864F-4BEC-E84C-8BC3-11680213E110}" name="Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A16:C17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A16:C17" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="7">
       <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
@@ -1841,13 +1892,13 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E16:F17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="E16:F17" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="2">
       <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Effort/Hour" dataDxfId="1">
       <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2176,20 +2227,20 @@
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -2215,7 +2266,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>85</v>
       </c>
@@ -2246,7 +2297,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>86</v>
       </c>
@@ -2255,29 +2306,29 @@
       </c>
       <c r="C3" s="7" cm="1">
         <f t="array" ref="C3">Tabelle38[Estimated time]</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" cm="1">
         <f t="array" ref="D3">Tabelle38[Actual time]</f>
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E3" s="7" cm="1">
         <f t="array" ref="E3">Tabelle49[[Total Storypoints ]]</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F3" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
-        <v>1.4444444444444444</v>
+        <v>0.875</v>
       </c>
       <c r="G3" s="7">
         <v>146</v>
       </c>
       <c r="H3" s="7">
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
@@ -2295,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>88</v>
       </c>
@@ -2313,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
@@ -2331,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
@@ -2349,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
@@ -2367,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>92</v>
       </c>
@@ -2375,16 +2426,16 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C13" s="5">
         <f>C12-SUM(Tabelle1[Accomplished Story Points])</f>
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>96</v>
       </c>
@@ -2393,31 +2444,31 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
-        <v>0.20634920634920634</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="14">
         <f>(SUM(Tabelle1[Accomplished Story Points],)/G2)</f>
-        <v>8.9041095890410954E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.14383561643835616</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="24" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="18">
         <f>C13/C15</f>
-        <v>644.53846153846155</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -2435,21 +2486,21 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -2481,7 +2532,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>45925</v>
       </c>
@@ -2511,7 +2562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -2533,7 +2584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
@@ -2553,7 +2604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2565,7 +2616,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
@@ -2593,7 +2644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
@@ -2619,7 +2670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
@@ -2643,7 +2694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2655,7 +2706,7 @@
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2667,7 +2718,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2679,7 +2730,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2691,7 +2742,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2703,7 +2754,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2715,7 +2766,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>108</v>
       </c>
@@ -2737,7 +2788,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <f>SUM(Tabelle2[Estimated time])</f>
         <v>13</v>
@@ -2780,18 +2831,18 @@
     <tabColor theme="6"/>
   </sheetPr>
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="61.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2815,7 +2866,7 @@
       </c>
       <c r="I1" s="17"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2839,7 +2890,7 @@
       </c>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2861,7 +2912,7 @@
       <c r="G3" s="2"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2883,7 +2934,7 @@
       <c r="G4" s="2"/>
       <c r="I4" s="17"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -2905,7 +2956,7 @@
       <c r="G5" s="2"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -2927,7 +2978,7 @@
       <c r="G6" s="2"/>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -2949,7 +3000,7 @@
       <c r="G7" s="2"/>
       <c r="I7" s="17"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -2971,7 +3022,7 @@
       <c r="G8" s="2"/>
       <c r="I8" s="17"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -2993,7 +3044,7 @@
       <c r="G9" s="2"/>
       <c r="I9" s="17"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -3015,7 +3066,7 @@
       <c r="G10" s="2"/>
       <c r="I10" s="17"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -3037,7 +3088,7 @@
       <c r="G11" s="2"/>
       <c r="I11" s="17"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
@@ -3059,7 +3110,7 @@
       <c r="G12" s="2"/>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -3081,7 +3132,7 @@
       <c r="G13" s="2"/>
       <c r="I13" s="17"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -3103,7 +3154,7 @@
       <c r="G14" s="2"/>
       <c r="I14" s="17"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -3125,7 +3176,7 @@
       <c r="G15" s="2"/>
       <c r="I15" s="17"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -3147,7 +3198,7 @@
       <c r="G16" s="2"/>
       <c r="I16" s="17"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
@@ -3169,7 +3220,7 @@
       <c r="G17" s="2"/>
       <c r="I17" s="17"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
@@ -3191,7 +3242,7 @@
       <c r="G18" s="2"/>
       <c r="I18" s="17"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
@@ -3213,7 +3264,7 @@
       <c r="G19" s="2"/>
       <c r="I19" s="17"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
@@ -3235,7 +3286,7 @@
       <c r="G20" s="2"/>
       <c r="I20" s="17"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
@@ -3249,15 +3300,17 @@
         <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="F21" s="2">
         <v>9</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
       <c r="I21" s="17"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
@@ -3279,7 +3332,7 @@
       <c r="G22" s="2"/>
       <c r="I22" s="17"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>66</v>
       </c>
@@ -3301,7 +3354,7 @@
       <c r="G23" s="2"/>
       <c r="I23" s="17"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
@@ -3323,7 +3376,7 @@
       <c r="G24" s="2"/>
       <c r="I24" s="17"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>72</v>
       </c>
@@ -3345,7 +3398,7 @@
       <c r="G25" s="2"/>
       <c r="I25" s="17"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>75</v>
       </c>
@@ -3367,7 +3420,7 @@
       <c r="G26" s="2"/>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="16"/>
       <c r="C27" s="4"/>
@@ -3393,22 +3446,23 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="124.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="164.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -3439,8 +3493,11 @@
       <c r="J1" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>45939</v>
       </c>
@@ -3471,8 +3528,11 @@
       <c r="J2" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K2" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -3497,8 +3557,11 @@
       <c r="J3" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K3" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3509,8 +3572,9 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
@@ -3537,8 +3601,9 @@
       <c r="J5" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
@@ -3561,8 +3626,11 @@
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K6" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3573,8 +3641,9 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3585,44 +3654,98 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="8">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8">
+        <v>15</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="8">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="8">
+        <v>3</v>
+      </c>
       <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K10" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="8">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="8">
+        <v>2</v>
+      </c>
       <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K11" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3633,8 +3756,9 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3646,7 +3770,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3658,54 +3782,66 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>110</v>
-      </c>
+    <row r="15" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>118</v>
-      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="12">
-        <f>SUM(Tabelle27[Estimated time])</f>
-        <v>12</v>
-      </c>
-      <c r="B16" s="12">
-        <f>SUM(Tabelle27[Time in Hours])</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="12">
-        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
-        <v>3</v>
+    <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="12">
-        <f>SUM(Tabelle27[Story points])</f>
-        <v>13</v>
-      </c>
-      <c r="F16" s="12">
-        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
-        <v>1.4444444444444444</v>
+      <c r="E16" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f>SUM(Tabelle27[Estimated time])</f>
+        <v>42</v>
+      </c>
+      <c r="B17" s="12">
+        <f>SUM(Tabelle27[Time in Hours])</f>
+        <v>24</v>
+      </c>
+      <c r="C17" s="12">
+        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
+        <v>18</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="12">
+        <f>SUM(Tabelle27[Story points])</f>
+        <v>21</v>
+      </c>
+      <c r="F17" s="12">
+        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
+        <v>0.875</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhoheneder/Desktop/Schule/syp/AquaSphere/Excel_File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C95B2-D4F4-7C4E-AC15-9845565D49EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC49298-A999-2444-9FBB-8B9B85418EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1340" yWindow="1020" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
@@ -674,20 +674,6 @@
   <dxfs count="62">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -886,6 +872,20 @@
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1867,23 +1867,23 @@
     <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
     <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="11"/>
     <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{EEDB864F-4BEC-E84C-8BC3-11680213E110}" name="Status" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{EEDB864F-4BEC-E84C-8BC3-11680213E110}" name="Status" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A16:C17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A16:C17" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A16:C17" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="6">
       <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="5">
       <calculatedColumnFormula>SUM(Tabelle27[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="4">
       <calculatedColumnFormula>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1892,13 +1892,13 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E16:F17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E16:F17" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="E16:F17" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="1">
       <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Effort/Hour" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Effort/Hour" dataDxfId="0">
       <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D3" s="7" cm="1">
         <f t="array" ref="D3">Tabelle38[Actual time]</f>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E3" s="7" cm="1">
         <f t="array" ref="E3">Tabelle49[[Total Storypoints ]]</f>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="F3" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
-        <v>0.875</v>
+        <v>0.61764705882352944</v>
       </c>
       <c r="G3" s="7">
         <v>146</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
-        <v>0.125</v>
+        <v>8.8235294117647065E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" x14ac:dyDescent="0.3">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C17" s="18">
         <f>C13/C15</f>
-        <v>1000</v>
+        <v>1416.6666666666665</v>
       </c>
     </row>
   </sheetData>
@@ -3711,9 +3711,11 @@
       <c r="I10" s="8">
         <v>3</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="8">
+        <v>10</v>
+      </c>
       <c r="K10" s="19" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
@@ -3823,11 +3825,11 @@
       </c>
       <c r="B17" s="12">
         <f>SUM(Tabelle27[Time in Hours])</f>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C17" s="12">
         <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="12">
@@ -3836,7 +3838,7 @@
       </c>
       <c r="F17" s="12">
         <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
-        <v>0.875</v>
+        <v>0.61764705882352944</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>

--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C83BDA-0CDC-466B-909D-6F92D22E2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F23E7AC-B093-404D-BC82-CD3281E9B18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
     <sheet name="Sprint1" sheetId="3" r:id="rId2"/>
-    <sheet name="Storys" sheetId="1" r:id="rId3"/>
-    <sheet name="Sprint2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sprint2" sheetId="4" r:id="rId3"/>
+    <sheet name="Storys" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -638,26 +638,6 @@
   <dxfs count="61">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1017,383 +997,6 @@
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -1512,6 +1115,383 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1542,6 +1522,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1720,14 +1720,14 @@
     <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="55">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="54">
       <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="54">
+    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="53">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="52">
+    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="51">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1736,35 +1736,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="36">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="27">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="35">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="34">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1773,13 +1773,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="31">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="30">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1788,51 +1788,35 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
-  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="10"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="6">
       <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="5">
       <calculatedColumnFormula>SUM(Tabelle27[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="4">
       <calculatedColumnFormula>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1840,16 +1824,32 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="1">
       <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="0">
       <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2775,620 +2775,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
-  <sheetPr>
-    <tabColor theme="6"/>
-  </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="I3" s="17"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="2">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="I4" s="17"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="2">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="2">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="I17" s="17"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="2">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="2">
-        <v>14</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="2">
-        <v>4</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="2">
-        <v>15</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="2">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="2">
-        <v>7</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="2">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="2">
-        <v>16</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2">
-        <v>7</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4">
-        <f>SUM(F2:F26)</f>
-        <v>146</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90405E51-A006-46BC-8B15-C0222E7D47D2}">
   <sheetPr>
     <tabColor theme="0"/>
@@ -3716,4 +3102,618 @@
     <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <f>SUM(F2:F26)</f>
+        <v>146</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhoheneder/Desktop/Schule/syp/AquaSphere/Excel_File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F23E7AC-B093-404D-BC82-CD3281E9B18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FA0BD0-7D72-DE4E-9119-DB7ACC598B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="2260" yWindow="1060" windowWidth="31120" windowHeight="19480" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
     <sheet name="Sprint1" sheetId="3" r:id="rId2"/>
-    <sheet name="Sprint2" sheetId="4" r:id="rId3"/>
-    <sheet name="Storys" sheetId="1" r:id="rId4"/>
+    <sheet name="Storys" sheetId="1" r:id="rId3"/>
+    <sheet name="Sprint2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="148">
   <si>
     <t>Story ID</t>
   </si>
@@ -475,13 +475,43 @@
   </si>
   <si>
     <t>Als Nutzer möchte "mein" Aquarium haben</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>Effort/Hour</t>
+  </si>
+  <si>
+    <t>Started / not done</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Backend mit Datenbank erstellen</t>
+  </si>
+  <si>
+    <t>Datenbank und Backend erstellt und einsatzbereit</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Zustand speichern und korrekt mit User verknüpfen</t>
+  </si>
+  <si>
+    <t>Zustände müssen universell für offline und online speicherung erstellt werden. Online zustände werden ans Backend übertragen und korrekt mit dem User abgespeichert</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Offline und Online zustände korrekt handlen</t>
+  </si>
+  <si>
+    <t>Wenn der User einsteigt wird überprüft welcher Speicherstand der aktuellste ist und dieser dann heruntergeladen / hochgeladen</t>
+  </si>
+  <si>
+    <t>in progress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +577,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -610,7 +646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -630,12 +666,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="62">
     <dxf>
       <font>
         <b val="0"/>
@@ -836,6 +873,20 @@
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1709,25 +1760,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
   <autoFilter ref="A1:H8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="57">
       <calculatedColumnFormula array="1">Tabelle3[Estimated time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="55">
+    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="56">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="54">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="55">
       <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="53">
+    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="54">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="51">
+    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="52">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1736,35 +1787,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="37">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="35">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="36">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="34">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="35">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1773,13 +1824,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="31">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="32">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="31">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1788,27 +1839,44 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:K12" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:K12" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{EEDB864F-4BEC-E84C-8BC3-11680213E110}" name="Status" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A16:C17" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A16:C17" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="6">
       <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
@@ -1824,32 +1892,16 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E16:F17" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="E16:F17" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="1">
       <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Effort/Hour" dataDxfId="0">
       <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2176,20 +2228,20 @@
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -2215,7 +2267,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>85</v>
       </c>
@@ -2246,7 +2298,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>86</v>
       </c>
@@ -2255,29 +2307,29 @@
       </c>
       <c r="C3" s="7" cm="1">
         <f t="array" ref="C3">Tabelle38[Estimated time]</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" cm="1">
         <f t="array" ref="D3">Tabelle38[Actual time]</f>
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E3" s="7" cm="1">
         <f t="array" ref="E3">Tabelle49[[Total Storypoints ]]</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F3" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
-        <v>1.4444444444444444</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="G3" s="7">
         <v>146</v>
       </c>
       <c r="H3" s="7">
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
@@ -2295,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>88</v>
       </c>
@@ -2313,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
@@ -2331,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
@@ -2349,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
@@ -2367,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>92</v>
       </c>
@@ -2375,16 +2427,16 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C13" s="5">
         <f>C12-SUM(Tabelle1[Accomplished Story Points])</f>
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>96</v>
       </c>
@@ -2393,31 +2445,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
-        <v>0.20634920634920634</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.10084033613445378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="14">
         <f>(SUM(Tabelle1[Accomplished Story Points],)/G2)</f>
-        <v>8.9041095890410954E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.16438356164383561</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="24" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="18">
         <f>C13/C15</f>
-        <v>644.53846153846155</v>
+        <v>1209.8333333333333</v>
+      </c>
+      <c r="D17">
+        <f>C17/3</f>
+        <v>403.27777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -2435,21 +2491,21 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="95.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -2481,7 +2537,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>45925</v>
       </c>
@@ -2511,7 +2567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -2533,7 +2589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
@@ -2553,7 +2609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2565,7 +2621,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
@@ -2593,7 +2649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
@@ -2619,7 +2675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
@@ -2643,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2655,7 +2711,7 @@
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2667,7 +2723,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2679,7 +2735,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2691,7 +2747,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2703,7 +2759,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2715,7 +2771,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>108</v>
       </c>
@@ -2737,7 +2793,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <f>SUM(Tabelle2[Estimated time])</f>
         <v>13</v>
@@ -2775,26 +2831,643 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="61.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="4"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <f>SUM(F2:F26)</f>
+        <v>146</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90405E51-A006-46BC-8B15-C0222E7D47D2}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="124.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="164.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -2825,8 +3498,11 @@
       <c r="J1" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>45939</v>
       </c>
@@ -2857,8 +3533,11 @@
       <c r="J2" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K2" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -2883,8 +3562,11 @@
       <c r="J3" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K3" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2895,8 +3577,9 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
@@ -2923,8 +3606,9 @@
       <c r="J5" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
@@ -2945,10 +3629,15 @@
       <c r="H6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8">
+        <v>5</v>
+      </c>
       <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K6" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2959,8 +3648,9 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2971,44 +3661,98 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="8">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8">
+        <v>15</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C10" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="8">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="8">
+        <v>3</v>
+      </c>
+      <c r="J10" s="8">
+        <v>10</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="8">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K11" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3019,8 +3763,9 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3032,7 +3777,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3044,54 +3789,66 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>110</v>
-      </c>
+    <row r="15" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>118</v>
-      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="12">
-        <f>SUM(Tabelle27[Estimated time])</f>
-        <v>12</v>
-      </c>
-      <c r="B16" s="12">
-        <f>SUM(Tabelle27[Time in Hours])</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="12">
-        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
-        <v>3</v>
+    <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="12">
-        <f>SUM(Tabelle27[Story points])</f>
-        <v>13</v>
-      </c>
-      <c r="F16" s="12">
-        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
-        <v>1.4444444444444444</v>
+      <c r="E16" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f>SUM(Tabelle27[Estimated time])</f>
+        <v>42</v>
+      </c>
+      <c r="B17" s="12">
+        <f>SUM(Tabelle27[Time in Hours])</f>
+        <v>34</v>
+      </c>
+      <c r="C17" s="12">
+        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
+        <v>8</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="12">
+        <f>SUM(Tabelle27[Story points])</f>
+        <v>24</v>
+      </c>
+      <c r="F17" s="12">
+        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3102,618 +3859,4 @@
     <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
-  <sheetPr>
-    <tabColor theme="6"/>
-  </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="I3" s="17"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="2">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="I4" s="17"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="2">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="2">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="I17" s="17"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="2">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="2">
-        <v>14</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="2">
-        <v>4</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="2">
-        <v>15</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="2">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="2">
-        <v>7</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="2">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="2">
-        <v>16</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2">
-        <v>7</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4">
-        <f>SUM(F2:F26)</f>
-        <v>146</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Excel_File/AquaSphare.xlsx
+++ b/Excel_File/AquaSphare.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43680\Desktop\Schule\SYP\Aquarium\Excel_File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F23E7AC-B093-404D-BC82-CD3281E9B18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25D955D-2FB8-4336-BFD9-48DE34521E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{3C511D28-10C8-4337-AED7-CFA66BBB7484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Dashboard" sheetId="2" r:id="rId1"/>
     <sheet name="Sprint1" sheetId="3" r:id="rId2"/>
     <sheet name="Sprint2" sheetId="4" r:id="rId3"/>
-    <sheet name="Storys" sheetId="1" r:id="rId4"/>
+    <sheet name="Sprint3" sheetId="5" r:id="rId4"/>
+    <sheet name="Storys" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="150">
   <si>
     <t>Story ID</t>
   </si>
@@ -475,13 +476,49 @@
   </si>
   <si>
     <t>Als Nutzer möchte "mein" Aquarium haben</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>Effort/Hour</t>
+  </si>
+  <si>
+    <t>Started / not done</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Backend mit Datenbank erstellen</t>
+  </si>
+  <si>
+    <t>Datenbank und Backend erstellt und einsatzbereit</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Zustand speichern und korrekt mit User verknüpfen</t>
+  </si>
+  <si>
+    <t>Zustände müssen universell für offline und online speicherung erstellt werden. Online zustände werden ans Backend übertragen und korrekt mit dem User abgespeichert</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich mein Aquarium geräteübergreifend synchronisieren. / Offline und Online zustände korrekt handlen</t>
+  </si>
+  <si>
+    <t>Wenn der User einsteigt wird überprüft welcher Speicherstand der aktuellste ist und dieser dann heruntergeladen / hochgeladen</t>
+  </si>
+  <si>
+    <t>in progress</t>
+  </si>
+  <si>
+    <t>AQ4</t>
+  </si>
+  <si>
+    <t>Als Nutzer möchte ich Steine und Korallen platzieren. Unterschiedliche Pflanzen sollen zur auswahl steten</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +584,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -610,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -630,12 +673,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="84">
     <dxf>
       <font>
         <b val="0"/>
@@ -836,6 +880,411 @@
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF0F9ED5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF0F9ED5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1709,25 +2158,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}" name="Tabelle1" displayName="Tabelle1" ref="A1:H8" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:H8" xr:uid="{AAF41172-5838-4CA9-A8A2-78B1E57ACF1F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{8BB8E342-544E-430C-A72A-9EBF9676D447}" name="Sprint" dataDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{96A939A8-DA63-4E70-B123-D31A897D4192}" name="Story ID" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{CB307D23-EE39-436B-9E06-9E7789362DB6}" name="Estimated Hours" dataDxfId="79">
       <calculatedColumnFormula array="1">Tabelle3[Estimated time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="55">
+    <tableColumn id="3" xr3:uid="{5EFC7DEC-DFDE-454B-90FC-2713EB4181D8}" name="Actual Hours" dataDxfId="78">
       <calculatedColumnFormula array="1">Tabelle3[Actual time]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="54">
+    <tableColumn id="4" xr3:uid="{D6FF0659-1B35-4F09-B5A7-D22FEF5F7C3F}" name="Accomplished Story Points" dataDxfId="77">
       <calculatedColumnFormula array="1">Tabelle4[[Total Storypoints ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="53">
+    <tableColumn id="5" xr3:uid="{9CD2DBE3-2E45-4440-8D7A-2A03A0291AAD}" name="Velocity" dataDxfId="76">
       <calculatedColumnFormula>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="51">
+    <tableColumn id="6" xr3:uid="{1977DF7A-0A05-43B5-99D3-B72159480780}" name="Total Storypoints" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{D8A5F5FE-B9BC-448A-A9E7-3D00888AE639}" name="Storypoints Left" dataDxfId="74">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1735,36 +2184,67 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0134C802-458D-4153-B0D4-D8B08E02E26A}" name="Tabelle4912" displayName="Tabelle4912" ref="E16:F17" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="E16:F17" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C3438C75-AD69-46E0-B1BD-0445ED469483}" name="Total Storypoints " dataDxfId="1">
+      <calculatedColumnFormula>SUM(Tabelle2710[Story points])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{0655740B-E1AB-4BD3-B7CA-852D4C79FC17}" name="Effort/Hour" dataDxfId="0">
+      <calculatedColumnFormula>Tabelle4912[[#This Row],[Total Storypoints ]]/Tabelle3811[[#This Row],[Actual time]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
+  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="44"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}" name="Tabelle2" displayName="Tabelle2" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
   <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{0351E8C1-0BB8-4C19-A406-233CC12328E5}" name="Sprint Start" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{51BD2FE0-507A-4398-BD96-E186E78BB2C7}" name="Sprint End" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{A3B7E86B-E01A-4D78-82AD-BA81F6AC7ADF}" name="User" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{CE780601-F45C-4063-B216-98ACE5588903}" name="ID" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{A14D049D-AC5C-49A5-A7CC-A4D5ED8A8330}" name="Epic" dataDxfId="67"/>
+    <tableColumn id="12" xr3:uid="{770F10A6-830A-41AC-B069-6267CAE00BDF}" name="User Story /Task" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{0D9AB552-F7B4-4231-A35B-245B57383919}" name="Estimated time" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{3E2E3644-9002-4AB9-B3EC-96FFF84D8900}" name="COS (Criteria of Satisfaction)" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{14C8E3A9-BC37-48D9-A399-32A48A46993A}" name="Story points" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{151786D9-5F15-42D7-932B-664A024F4131}" name="Time in Hours" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}" name="Tabelle3" displayName="Tabelle3" ref="A15:C16" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
   <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{CD2D4D96-DD34-4EA3-92D7-B02BB9DE5647}" name="Estimated time" dataDxfId="59">
       <calculatedColumnFormula>SUM(Tabelle2[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="35">
+    <tableColumn id="2" xr3:uid="{0F14E190-6E0A-4AB8-8ADE-83875E98D4B5}" name="Actual time" dataDxfId="58">
       <calculatedColumnFormula>SUM(Tabelle2[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="34">
+    <tableColumn id="3" xr3:uid="{5DE18543-F4D3-4732-9F2D-5B7F140CB974}" name="Delta" dataDxfId="57">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Estimated time]]-Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1773,13 +2253,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}" name="Tabelle4" displayName="Tabelle4" ref="E15:F16" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="31">
+    <tableColumn id="1" xr3:uid="{2E187AEA-682F-4749-9FC8-ED3BA3DE1DA2}" name="Total Storypoints " dataDxfId="54">
       <calculatedColumnFormula>SUM(Tabelle2[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{3C6DC8F5-724A-43AC-9128-7661A96380C1}" name="Efford/Hour" dataDxfId="53">
       <calculatedColumnFormula>Tabelle4[[#This Row],[Total Storypoints ]]/Tabelle3[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1788,35 +2268,36 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:J9" insertRowShift="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:J9" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A211D33B-248F-4E66-AF7C-9632EAA38DAC}" name="Tabelle27" displayName="Tabelle27" ref="A1:K12" insertRowShift="1" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+  <autoFilter ref="A1:K12" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{9C36A560-9153-4D8E-BA50-0044E74E1896}" name="Sprint Start" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{4FAB3106-8621-41F1-B866-EA5558F083D8}" name="Sprint End" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{2D2022CC-B165-4671-9773-4C7DCE737FC7}" name="User" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{6D49D607-DA69-4FF5-AC26-260E9F796217}" name="ID" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{95077F2F-115F-484E-A38C-A34A2BCBCB78}" name="Epic" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{2EAFDE91-2C58-4973-A684-28E2E964F629}" name="User Story /Task" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{D17AAC02-918A-4F08-B037-3622F37B62F0}" name="Estimated time" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{4D053EE2-698A-4191-ABEB-8F0701DA4D4E}" name="COS (Criteria of Satisfaction)" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{73BF0134-792D-4614-95FB-754C4A317665}" name="Story points" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{2620A9CC-A288-4874-BF27-2BBE69671B14}" name="Time in Hours" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{EEDB864F-4BEC-E84C-8BC3-11680213E110}" name="Status" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A15:C16" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A15:C16" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7635EDC6-25C8-4AEE-8477-EE4C813DEB0C}" name="Tabelle38" displayName="Tabelle38" ref="A16:C17" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A16:C17" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{608DD481-0706-4498-AF85-EB4AD6D17A03}" name="Estimated time" dataDxfId="28">
       <calculatedColumnFormula>SUM(Tabelle27[Estimated time])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{727CC20C-885F-49B6-A31D-85E6D39BFD35}" name="Actual time" dataDxfId="27">
       <calculatedColumnFormula>SUM(Tabelle27[Time in Hours])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{DB626F11-D2AA-4B08-BE29-BA7526E2BE88}" name="Delta" dataDxfId="26">
       <calculatedColumnFormula>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1825,13 +2306,13 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E15:F16" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="E15:F16" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{96D8EE75-69AD-457A-99FC-A0696238BDE6}" name="Tabelle49" displayName="Tabelle49" ref="E16:F17" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="E16:F17" xr:uid="{F5FF718A-3E4E-40DD-BD72-E3ACE1B58735}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{1F43F730-E2EB-4487-8A5C-6B0E3F4CC598}" name="Total Storypoints " dataDxfId="23">
       <calculatedColumnFormula>SUM(Tabelle27[Story points])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Efford/Hour" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{95E1605C-A4E2-4173-B0AE-218EC74BDEA1}" name="Effort/Hour" dataDxfId="22">
       <calculatedColumnFormula>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1840,16 +2321,38 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}" name="Tabelle5" displayName="Tabelle5" ref="A1:G27" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A1:G27" xr:uid="{9C26F5F1-3CA5-4498-8D9F-A792FBE4E032}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BC6E6F54-B9E2-4D1B-BB78-E6F30265832D}" name="Story ID" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{5BD6C059-22C9-4C4A-90A3-74736AC1F83D}" name="Title" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{F3A7207B-9229-4096-9A5B-C4FB1EDD5455}" name="Priority" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{E38B598E-699A-460C-AB30-1E65BB7404BF}" name="Effort" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{5087B805-D2DF-49C7-9936-ECACDF516D64}" name="Status" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{05DFD049-144E-4717-9B70-2B02AA12CC20}" name="Story Points" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{98F7F45D-928E-4B6F-868A-18B3899C12B6}" name="Sprint" dataDxfId="21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6303AB7F-CDC2-408B-A450-96D692A68B43}" name="Tabelle2710" displayName="Tabelle2710" ref="A1:K12" insertRowShift="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:K12" xr:uid="{739F99A6-83FF-4FC0-82EE-54F2B8B8AE5A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{949CA967-02A0-4249-BB07-B02F4C4F69AE}" name="Sprint Start" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A70AE104-D3DD-4C6E-8E50-E151404B19BD}" name="Sprint End" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{9168C6BE-6970-4420-9D5F-DBCF1E8E2BAE}" name="User" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A7C4968E-9480-42FF-949B-9E41609C26A2}" name="ID" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{8564B7DD-8DB4-4E2B-BDDB-9791D9AAA0EA}" name="Epic" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{56FA47CB-3810-4B7F-A047-8358D5C73F6C}" name="User Story /Task" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{988CB3AF-F268-445B-887C-5163D9AE41DF}" name="Estimated time" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{14BDCFB4-F75D-4798-AFF3-3F8B177B78D6}" name="COS (Criteria of Satisfaction)" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{97C18CBF-2D3F-4A8A-B36D-6328E17F31C4}" name="Story points" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{D3E339CF-38BF-4AC1-8C80-41ECD30B6907}" name="Time in Hours" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{3BCBC0DA-7C9B-4D2B-9269-A319CBD925C5}" name="Status" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C1E761E2-D340-4C7F-A19A-AE84A76F5971}" name="Tabelle3811" displayName="Tabelle3811" ref="A16:C17" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A16:C17" xr:uid="{F79F1E8C-9DFD-4482-95C6-9C23936D055B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F045D4AD-2D00-44A7-8EA7-B5C34869B26F}" name="Estimated time" dataDxfId="6">
+      <calculatedColumnFormula>SUM(Tabelle2710[Estimated time])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{DFDFE0A8-6207-4F3B-9D05-4D3AF083E31B}" name="Actual time" dataDxfId="5">
+      <calculatedColumnFormula>SUM(Tabelle2710[Time in Hours])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{2529739A-9C5E-4AE4-80A6-DFC080EFE2D8}" name="Delta" dataDxfId="4">
+      <calculatedColumnFormula>Tabelle3811[[#This Row],[Estimated time]]-Tabelle3811[[#This Row],[Actual time]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2178,15 +2681,15 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.5">
@@ -2255,36 +2758,47 @@
       </c>
       <c r="C3" s="7" cm="1">
         <f t="array" ref="C3">Tabelle38[Estimated time]</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" cm="1">
         <f t="array" ref="D3">Tabelle38[Actual time]</f>
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E3" s="7" cm="1">
         <f t="array" ref="E3">Tabelle49[[Total Storypoints ]]</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F3" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
-        <v>1.4444444444444444</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="G3" s="7">
         <v>146</v>
       </c>
       <c r="H3" s="7">
         <f>Tabelle1[[#This Row],[Total Storypoints]]-Tabelle1[[#This Row],[Accomplished Story Points]]</f>
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" cm="1">
+        <f t="array" ref="C4">Tabelle3811[Estimated time]</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="7" cm="1">
+        <f t="array" ref="D4">Tabelle3811[Actual time]</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" cm="1">
+        <f t="array" ref="E4">Tabelle4912[[Total Storypoints ]]</f>
+        <v>0</v>
+      </c>
       <c r="F4" s="7">
         <f>IFERROR(Tabelle1[[#This Row],[Accomplished Story Points]]/Tabelle1[[#This Row],[Actual Hours]],0)</f>
         <v>0</v>
@@ -2381,7 +2895,7 @@
       </c>
       <c r="C13" s="5">
         <f>C12-SUM(Tabelle1[Accomplished Story Points])</f>
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -2399,7 +2913,7 @@
       </c>
       <c r="C15" s="5">
         <f>AVERAGE(Tabelle1[Velocity])</f>
-        <v>0.20634920634920634</v>
+        <v>0.10084033613445378</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -2408,16 +2922,20 @@
       </c>
       <c r="C16" s="14">
         <f>(SUM(Tabelle1[Accomplished Story Points],)/G2)</f>
-        <v>8.9041095890410954E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0.16438356164383561</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="18">
         <f>C13/C15</f>
-        <v>644.53846153846155</v>
+        <v>1209.8333333333333</v>
+      </c>
+      <c r="D17">
+        <f>C17/3</f>
+        <v>403.27777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -2437,16 +2955,16 @@
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
@@ -2779,22 +3297,23 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="95.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="124.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="164.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -2825,8 +3344,11 @@
       <c r="J1" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
         <v>45939</v>
       </c>
@@ -2857,8 +3379,11 @@
       <c r="J2" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K2" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -2883,8 +3408,11 @@
       <c r="J3" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K3" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2895,8 +3423,9 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
@@ -2923,8 +3452,9 @@
       <c r="J5" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
@@ -2945,10 +3475,15 @@
       <c r="H6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8">
+        <v>5</v>
+      </c>
       <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K6" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2959,8 +3494,9 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2971,44 +3507,98 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="8">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8">
+        <v>15</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C10" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="8">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="8">
+        <v>3</v>
+      </c>
+      <c r="J10" s="8">
+        <v>10</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="8">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K11" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3019,8 +3609,9 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3032,7 +3623,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3044,54 +3635,66 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>110</v>
-      </c>
+    <row r="15" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>118</v>
-      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="12">
-        <f>SUM(Tabelle27[Estimated time])</f>
-        <v>12</v>
-      </c>
-      <c r="B16" s="12">
-        <f>SUM(Tabelle27[Time in Hours])</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="12">
-        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
-        <v>3</v>
+    <row r="16" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="12">
-        <f>SUM(Tabelle27[Story points])</f>
-        <v>13</v>
-      </c>
-      <c r="F16" s="12">
-        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
-        <v>1.4444444444444444</v>
+      <c r="E16" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="12">
+        <f>SUM(Tabelle27[Estimated time])</f>
+        <v>42</v>
+      </c>
+      <c r="B17" s="12">
+        <f>SUM(Tabelle27[Time in Hours])</f>
+        <v>34</v>
+      </c>
+      <c r="C17" s="12">
+        <f>Tabelle38[[#This Row],[Estimated time]]-Tabelle38[[#This Row],[Actual time]]</f>
+        <v>8</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="12">
+        <f>SUM(Tabelle27[Story points])</f>
+        <v>24</v>
+      </c>
+      <c r="F17" s="12">
+        <f>Tabelle49[[#This Row],[Total Storypoints ]]/Tabelle38[[#This Row],[Actual time]]</f>
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3105,6 +3708,317 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2267EA60-D88B-4605-AB26-1D6E6A658B46}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="124.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="164.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>45953</v>
+      </c>
+      <c r="B2" s="9">
+        <v>45967</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8">
+        <v>5</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="19"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="19"/>
+    </row>
+    <row r="10" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="19"/>
+    </row>
+    <row r="11" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="19"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="12">
+        <f>SUM(Tabelle2710[Estimated time])</f>
+        <v>5</v>
+      </c>
+      <c r="B17" s="12">
+        <f>SUM(Tabelle2710[Time in Hours])</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <f>Tabelle3811[[#This Row],[Estimated time]]-Tabelle3811[[#This Row],[Actual time]]</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="12">
+        <f>SUM(Tabelle2710[Story points])</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="e">
+        <f>Tabelle4912[[#This Row],[Total Storypoints ]]/Tabelle3811[[#This Row],[Actual time]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7C2A55-0520-4EB5-86E6-237FE14873A1}">
   <sheetPr>
     <tabColor theme="6"/>
@@ -3112,11 +4026,11 @@
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="4" max="4" width="61.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -3579,12 +4493,14 @@
         <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="F21" s="2">
         <v>9</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
       <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
